--- a/output/pdf_financials_xlsx/AVNT.xlsx
+++ b/output/pdf_financials_xlsx/AVNT.xlsx
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005861</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.023652</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.923743</v>
+        <v>-0.929604</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-12.950356</v>
+        <v>-12.974008</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-9.769</v>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.923743</v>
+        <v>-0.929604</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-12.950356</v>
+        <v>-12.974008</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-9.769</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-22328.2</v>
+        <v>-22368.97931034483</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-410.1175482787573</v>
@@ -2092,19 +2092,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.061822</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.148361</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002784</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.119203</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.019178</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>2.442246</v>
@@ -2122,13 +2122,13 @@
         <v>6.764</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="35">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.061822</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.148361</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002784</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.119203</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.019178</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.442246</v>
@@ -2214,13 +2214,13 @@
         <v>6.78</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.022</v>
+        <v>0.794</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="37">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.061822</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.148361</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2766,13 +2766,13 @@
         <v>5.837</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.416</v>
+        <v>9.644</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>9.404</v>
+        <v>7.664</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.671</v>
+        <v>6.186</v>
       </c>
     </row>
     <row r="49">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -49733,7 +49733,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">

--- a/output/pdf_financials_xlsx/AVNT.xlsx
+++ b/output/pdf_financials_xlsx/AVNT.xlsx
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -29765,7 +29765,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
